--- a/output/full_scan/batch_seq7_2026-08-21.xlsx
+++ b/output/full_scan/batch_seq7_2026-08-21.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -580,21 +580,21 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6666</v>
+        <v>6716</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>848.9525566859535</v>
+        <v>851.9653157007461</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>44.3</v>
+        <v>133</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>55.41607154097779</v>
+        <v>75.15128185240533</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>23.64384303693825</v>
+        <v>35.48066578797559</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.491801132107063</v>
+        <v>1.110189392587125</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,48 +623,48 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0281807847970579</v>
+        <v>4.502797046557952</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6588</v>
+        <v>6666</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>836.0647572914007</v>
+        <v>848.9525566859535</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>101</v>
+        <v>44.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>60.69782151475099</v>
+        <v>55.41607154097779</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18.93871101954385</v>
+        <v>23.64384303693825</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.375501523572612</v>
+        <v>3.491801132107063</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.197200024546033</v>
+        <v>0.0281807847970579</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6532</v>
+        <v>6588</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>835.7148040886777</v>
+        <v>836.0647572914007</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>87.40000000000001</v>
+        <v>101</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>62.14653651408332</v>
+        <v>60.69782151475099</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28.22798224901882</v>
+        <v>18.93871101954385</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.051813843291945</v>
+        <v>1.375501523572612</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.777653947296369</v>
+        <v>1.197200024546033</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6538</v>
+        <v>6532</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>826.6336698762451</v>
+        <v>835.7148040886777</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>194</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>73.54220062993498</v>
+        <v>62.14653651408332</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>31.33720366222651</v>
+        <v>28.22798224901882</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.263366987624516</v>
+        <v>2.051813843291945</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.592248148466755</v>
+        <v>1.777653947296369</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6727</v>
+        <v>6538</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>774.1300667732404</v>
+        <v>826.6336698762451</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>460</v>
+        <v>194</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.61321370968562</v>
+        <v>73.54220062993498</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>18.63525218613998</v>
+        <v>31.33720366222651</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.931553779003744</v>
+        <v>1.263366987624516</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>12.69459106132142</v>
+        <v>4.592248148466755</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6584</v>
+        <v>6727</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>771.8837080817493</v>
+        <v>774.1300667732404</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>586</v>
+        <v>460</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>54.2123271659782</v>
+        <v>59.61321370968562</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25.85805581758128</v>
+        <v>18.63525218613998</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6993811212971854</v>
+        <v>1.931553779003744</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>15.93543800006333</v>
+        <v>12.69459106132142</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6741</v>
+        <v>6584</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>736.678024345397</v>
+        <v>771.8837080817493</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>55</v>
+        <v>586</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,69 +923,69 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>42.96365806269708</v>
+        <v>54.2123271659782</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>26.74708015531327</v>
+        <v>25.85805581758128</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.002755747225595</v>
+        <v>0.6993811212971854</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1263108347970074</v>
+        <v>15.93543800006333</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6771</v>
+        <v>6741</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>724.134322469166</v>
+        <v>736.678024345397</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>77.87673930677855</v>
+        <v>42.96365806269708</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>37.32643941295602</v>
+        <v>26.74708015531327</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.513432246916603</v>
+        <v>2.002755747225595</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4809270615996589</v>
+        <v>0.1263108347970074</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6796</v>
+        <v>6771</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>717.1730372570513</v>
+        <v>724.134322469166</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>65.3</v>
+        <v>43</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>70.61565201025959</v>
+        <v>77.87673930677855</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.70213185725731</v>
+        <v>37.32643941295602</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.317303725705126</v>
+        <v>1.513432246916603</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,48 +1047,48 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.732133612482598</v>
+        <v>0.4809270615996589</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6512</v>
+        <v>6796</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>673.5875687658719</v>
+        <v>717.1730372570513</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>20.45</v>
+        <v>65.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>53.07067216696519</v>
+        <v>70.61565201025959</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>8.208781603126617</v>
+        <v>25.70213185725731</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.068709607594545</v>
+        <v>3.317303725705126</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.5900509791539339</v>
+        <v>0.732133612482598</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6517</v>
+        <v>6512</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>664.6690628692667</v>
+        <v>673.5875687658719</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>66.7</v>
+        <v>20.45</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>52.87417247545801</v>
+        <v>53.07067216696519</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15.23120735112618</v>
+        <v>8.208781603126617</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6454365271410938</v>
+        <v>2.068709607594545</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,48 +1153,48 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.6672873001251438</v>
+        <v>0.5900509791539339</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6674</v>
+        <v>6517</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>663.431442742377</v>
+        <v>664.6690628692667</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16.3</v>
+        <v>66.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>59.62006678215166</v>
+        <v>52.87417247545801</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>28.27073888885115</v>
+        <v>15.23120735112618</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6.277365140926665</v>
+        <v>0.6454365271410938</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,51 +1206,51 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.1506922628350329</v>
+        <v>0.6672873001251438</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6651</v>
+        <v>6674</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>662.8125342374776</v>
+        <v>663.431442742377</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>139.5</v>
+        <v>16.3</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.15668369898003</v>
+        <v>59.62006678215166</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>20.48547600892265</v>
+        <v>28.27073888885115</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6351142792348287</v>
+        <v>6.277365140926665</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,51 +1259,51 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.006523717579036</v>
+        <v>0.1506922628350329</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6672</v>
+        <v>6651</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>661.8955776073154</v>
+        <v>662.8125342374776</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>267.5</v>
+        <v>139.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.58977890336608</v>
+        <v>57.15668369898003</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>23.22650523961997</v>
+        <v>20.48547600892265</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.574212231090686</v>
+        <v>0.6351142792348287</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>5.406466489128807</v>
+        <v>2.006523717579036</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6830</v>
+        <v>6672</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>635.8209385948219</v>
+        <v>661.8955776073154</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>462</v>
+        <v>267.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>58.2521055439471</v>
+        <v>55.58977890336608</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>17.18576591451595</v>
+        <v>23.22650523961997</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.101540560486299</v>
+        <v>1.574212231090686</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,51 +1365,51 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>9.269706953261164</v>
+        <v>5.406466489128807</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6720</v>
+        <v>6830</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>617.5895204001876</v>
+        <v>635.8209385948219</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>138.5</v>
+        <v>462</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G18" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>51.32785547893779</v>
+        <v>58.2521055439471</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.36019876332734</v>
+        <v>17.18576591451595</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8927475532682307</v>
+        <v>2.101540560486299</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.3809433590758644</v>
+        <v>9.269706953261164</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6763</v>
+        <v>6720</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>609.8913258445771</v>
+        <v>617.5895204001876</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>41.9</v>
+        <v>138.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>42.3063965088534</v>
+        <v>51.32785547893779</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.4087063858788</v>
+        <v>22.36019876332734</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4574583394609614</v>
+        <v>0.8927475532682307</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0855440546871698</v>
+        <v>0.3809433590758644</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6680</v>
+        <v>6763</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>593.2857577556673</v>
+        <v>609.8913258445771</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>51.9</v>
+        <v>41.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>51.51480832256394</v>
+        <v>42.3063965088534</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>8.532754951620182</v>
+        <v>23.4087063858788</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.102217205993733</v>
+        <v>0.4574583394609614</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1393799794291657</v>
+        <v>0.0855440546871698</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6577</v>
+        <v>6680</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>589.1569855477193</v>
+        <v>593.2857577556673</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>80.7</v>
+        <v>51.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>51.92226970318072</v>
+        <v>51.51480832256394</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>24.28288398681965</v>
+        <v>8.532754951620182</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.06550394986102211</v>
+        <v>1.102217205993733</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,48 +1577,48 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.0475868050687925</v>
+        <v>0.1393799794291657</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6669</v>
+        <v>6577</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>576.1430413448553</v>
+        <v>589.1569855477193</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>6255</v>
+        <v>80.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G22" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.94329350056613</v>
+        <v>51.92226970318072</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25.65267232421449</v>
+        <v>24.28288398681965</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4213981437138206</v>
+        <v>0.06550394986102211</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,51 +1630,51 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>2.717626975666519</v>
+        <v>-0.0475868050687925</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6692</v>
+        <v>6669</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>574.334159945088</v>
+        <v>576.1430413448553</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>24.25</v>
+        <v>6255</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.2041058100463</v>
+        <v>58.94329350056613</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9.789370174735131</v>
+        <v>25.65267232421449</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.196964041308946</v>
+        <v>0.4213981437138206</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.3622683471872001</v>
+        <v>2.717626975666519</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6498</v>
+        <v>6692</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>573.3844436696808</v>
+        <v>574.334159945088</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>75.8</v>
+        <v>24.25</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45.32393953459287</v>
+        <v>52.2041058100463</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.92240929655222</v>
+        <v>9.789370174735131</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2031410054582093</v>
+        <v>1.196964041308946</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,51 +1736,51 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.9143783277835684</v>
+        <v>0.3622683471872001</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6491</v>
+        <v>6498</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>571.4359482790105</v>
+        <v>573.3844436696808</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>372</v>
+        <v>75.8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>58.2268006524362</v>
+        <v>45.32393953459287</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.53795522918016</v>
+        <v>29.92240929655222</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3815469879171571</v>
+        <v>0.2031410054582093</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,137 +1789,137 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0847353195573292</v>
+        <v>0.9143783277835684</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6510</v>
+        <v>6491</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>565.5956296142853</v>
+        <v>571.4359482790105</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2760</v>
+        <v>372</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>48.70926676175798</v>
+        <v>58.2268006524362</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16.45146790134639</v>
+        <v>24.53795522918016</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.8146075402680437</v>
+        <v>0.3815469879171571</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>21.86370520619538</v>
+        <v>-0.0847353195573292</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6605</v>
+        <v>6510</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>558.2689832849611</v>
+        <v>565.5956296142853</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>141.5</v>
+        <v>2760</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>60.12191295763597</v>
+        <v>48.70926676175798</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>14.01497041891781</v>
+        <v>16.45146790134639</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5440713793990677</v>
+        <v>0.8146075402680437</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.6354719942822089</v>
+        <v>21.86370520619538</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6505</v>
+        <v>6605</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>556.5069132280407</v>
+        <v>558.2689832849611</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>75.8</v>
+        <v>141.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>59.2647708202864</v>
+        <v>60.12191295763597</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>28.44902726317902</v>
+        <v>14.01497041891781</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7250117289215797</v>
+        <v>0.5440713793990677</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0718694488340365</v>
+        <v>0.6354719942822089</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6589</v>
+        <v>6505</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>540.550069135803</v>
+        <v>556.5069132280407</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>51.2</v>
+        <v>75.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>58.44505968060386</v>
+        <v>59.2647708202864</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.17675906197842</v>
+        <v>28.44902726317902</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.948644093886122</v>
+        <v>0.7250117289215797</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,154 +2001,154 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.176942084306564</v>
+        <v>-0.0718694488340365</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6488</v>
+        <v>6589</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>537.5403922126548</v>
+        <v>540.550069135803</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>993</v>
+        <v>51.2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>49.50631304546148</v>
+        <v>58.44505968060386</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15.64196982531806</v>
+        <v>28.17675906197842</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8473473616567363</v>
+        <v>0.948644093886122</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>16.40520556519307</v>
+        <v>0.176942084306564</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6805</v>
+        <v>6488</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>533.729488954733</v>
+        <v>537.5403922126548</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1765</v>
+        <v>993</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.40290502197696</v>
+        <v>49.50631304546148</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>27.47347004041428</v>
+        <v>15.64196982531806</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4618906594001837</v>
+        <v>0.8473473616567363</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>17.98840462726969</v>
+        <v>16.40520556519307</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6806</v>
+        <v>6805</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>533.729488954733</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>3.51</v>
+        <v>1765</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>31.69502562538877</v>
+        <v>54.40290502197696</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>32.59320088566449</v>
+        <v>27.47347004041428</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.4618906594001837</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,48 +2160,48 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4112821391126249</v>
+        <v>17.98840462726969</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6494</v>
+        <v>6806</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>526.7642077328245</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>55.2</v>
+        <v>3.51</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.68105279649274</v>
+        <v>31.69502562538877</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>16.951381779156</v>
+        <v>32.59320088566449</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6161677291293116</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,48 +2213,48 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.8534745571605866</v>
+        <v>0.4112821391126249</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6533</v>
+        <v>6494</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>526.3631459427594</v>
+        <v>526.7642077328245</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>250</v>
+        <v>55.2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>60.42295123896984</v>
+        <v>53.68105279649274</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>12.95267166034341</v>
+        <v>16.951381779156</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.2814763151286938</v>
+        <v>0.6161677291293116</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1477774412010362</v>
+        <v>0.8534745571605866</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6582</v>
+        <v>6533</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>525.1239225556296</v>
+        <v>526.3631459427594</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>32.7</v>
+        <v>250</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>59.38558621807651</v>
+        <v>60.42295123896984</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14.50809497766491</v>
+        <v>12.95267166034341</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.498072000391306</v>
+        <v>0.2814763151286938</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0780360554567338</v>
+        <v>0.1477774412010362</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6598</v>
+        <v>6582</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>522.6527394027481</v>
+        <v>525.1239225556296</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>28.55</v>
+        <v>32.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>53.19828659478073</v>
+        <v>59.38558621807651</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.49822844412074</v>
+        <v>14.50809497766491</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5408140510617286</v>
+        <v>1.498072000391306</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.3149778983636986</v>
+        <v>0.0780360554567338</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6770</v>
+        <v>6598</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>503.1075286757636</v>
+        <v>522.6527394027481</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>68.40000000000001</v>
+        <v>28.55</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>50.85479931453187</v>
+        <v>53.19828659478073</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.51684765941259</v>
+        <v>23.49822844412074</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5048558768824</v>
+        <v>0.5408140510617286</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4983077189200198</v>
+        <v>-0.3149778983636986</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6715</v>
+        <v>6770</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>501.7436989901729</v>
+        <v>503.1075286757636</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>448</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>58.03582560372821</v>
+        <v>50.85479931453187</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>17.30347027548845</v>
+        <v>13.51684765941259</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.974369899017288</v>
+        <v>0.5048558768824</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>14.67310215038643</v>
+        <v>0.4983077189200198</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6753</v>
+        <v>6715</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>497.2626404904765</v>
+        <v>501.7436989901729</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>141.5</v>
+        <v>448</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>50.86171724590641</v>
+        <v>58.03582560372821</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>24.24456672169867</v>
+        <v>17.30347027548845</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3826522776719056</v>
+        <v>1.974369899017288</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.4366995204256199</v>
+        <v>14.67310215038643</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6670</v>
+        <v>6753</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>496.369885359575</v>
+        <v>497.2626404904765</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>268.5</v>
+        <v>141.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>55.28640906433377</v>
+        <v>50.86171724590641</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>13.13013341390128</v>
+        <v>24.24456672169867</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.493810410294332</v>
+        <v>0.3826522776719056</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,48 +2584,48 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.4485371158892302</v>
+        <v>0.4366995204256199</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6597</v>
+        <v>6670</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>493.3304480335721</v>
+        <v>496.369885359575</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>72</v>
+        <v>268.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G41" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52.65844920190874</v>
+        <v>55.28640906433377</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>8.374301663924285</v>
+        <v>13.13013341390128</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.789109437980075</v>
+        <v>0.493810410294332</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,48 +2637,48 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>3.250452009934261</v>
+        <v>0.4485371158892302</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6756</v>
+        <v>6597</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>490.15530514551</v>
+        <v>493.3304480335721</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G42" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.9129049515354</v>
+        <v>52.65844920190874</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>12.39366776610537</v>
+        <v>8.374301663924285</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3691000932631028</v>
+        <v>1.789109437980075</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,51 +2690,51 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0057285570076435</v>
+        <v>3.250452009934261</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6803</v>
+        <v>6756</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>469.1834238882283</v>
+        <v>490.15530514551</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>269</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G43" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>41.14023454737551</v>
+        <v>51.9129049515354</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>31.3851393673851</v>
+        <v>12.39366776610537</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7269950732728416</v>
+        <v>0.3691000932631028</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.3276989198755693</v>
+        <v>0.0057285570076435</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6708</v>
+        <v>6803</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>457.839496229121</v>
+        <v>469.1834238882283</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>38.65</v>
+        <v>269</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.70401818261571</v>
+        <v>41.14023454737551</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>9.928666492920096</v>
+        <v>31.3851393673851</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.143605800190971</v>
+        <v>0.7269950732728416</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.59381269303038</v>
+        <v>0.3276989198755693</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6821</v>
+        <v>6708</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>455.1837629696275</v>
+        <v>457.839496229121</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>41.5</v>
+        <v>38.65</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>40.37940150397679</v>
+        <v>51.70401818261571</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>24.95526090219068</v>
+        <v>9.928666492920096</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4632256053305758</v>
+        <v>1.143605800190971</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,51 +2849,51 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.6863140330619548</v>
+        <v>1.59381269303038</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6645</v>
+        <v>6821</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>454.2125727586646</v>
+        <v>455.1837629696275</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>13.05</v>
+        <v>41.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G46" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>42.78061675192389</v>
+        <v>40.37940150397679</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>26.64139198116777</v>
+        <v>24.95526090219068</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2853094609390095</v>
+        <v>0.4632256053305758</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,48 +2902,48 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0019139979355416</v>
+        <v>0.6863140330619548</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6788</v>
+        <v>6645</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>449.9544576436092</v>
+        <v>454.2125727586646</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>348.5</v>
+        <v>13.05</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G47" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>44.86841752388892</v>
+        <v>42.78061675192389</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.9976665777477</v>
+        <v>26.64139198116777</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5247569084160194</v>
+        <v>0.2853094609390095</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,48 +2955,48 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>3.397374100853874</v>
+        <v>0.0019139979355416</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6831</v>
+        <v>6788</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>438.72745525834</v>
+        <v>449.9544576436092</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>574</v>
+        <v>348.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G48" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>41.50337208286501</v>
+        <v>44.86841752388892</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>17.27291591424903</v>
+        <v>25.9976665777477</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.912086657632698</v>
+        <v>0.5247569084160194</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.216001512542803</v>
+        <v>3.397374100853874</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6807</v>
+        <v>6831</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>433.1842639400383</v>
+        <v>438.72745525834</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>38</v>
+        <v>574</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>67.40418550019379</v>
+        <v>41.50337208286501</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>17.69384080806922</v>
+        <v>17.27291591424903</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6713489520204117</v>
+        <v>0.912086657632698</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,48 +3061,48 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0563642776316808</v>
+        <v>1.216001512542803</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6624</v>
+        <v>6807</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>429.7956681600365</v>
+        <v>433.1842639400383</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>41.05</v>
+        <v>38</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G50" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>53.01157832544785</v>
+        <v>67.40418550019379</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8.178099776686743</v>
+        <v>17.69384080806922</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.0326750252803655</v>
+        <v>0.6713489520204117</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,48 +3114,48 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.334004975177323</v>
+        <v>0.0563642776316808</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6834</v>
+        <v>6624</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>428.5417897391538</v>
+        <v>429.7956681600365</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>89.7</v>
+        <v>41.05</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>44.13662197918937</v>
+        <v>53.01157832544785</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>14.49211749798993</v>
+        <v>8.178099776686743</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5219037492251735</v>
+        <v>0.0326750252803655</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.07595093374472719</v>
+        <v>1.334004975177323</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6782</v>
+        <v>6834</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>427.3261546845108</v>
+        <v>428.5417897391538</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>202</v>
+        <v>89.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.6405466773053</v>
+        <v>44.13662197918937</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.59501606604016</v>
+        <v>14.49211749798993</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.3900362762751961</v>
+        <v>0.5219037492251735</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0378425543499743</v>
+        <v>-0.07595093374472719</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6789</v>
+        <v>6782</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>426.3538279681254</v>
+        <v>427.3261546845108</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>424</v>
+        <v>202</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>42.32029475059587</v>
+        <v>52.6405466773053</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>23.63622779137715</v>
+        <v>20.59501606604016</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3611462343792964</v>
+        <v>0.3900362762751961</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.041070616326451</v>
+        <v>0.0378425543499743</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6526</v>
+        <v>6789</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>424.5874808937812</v>
+        <v>426.3538279681254</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>572</v>
+        <v>424</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>42.82993963588281</v>
+        <v>42.32029475059587</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.0320740204058</v>
+        <v>23.63622779137715</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8205686937221662</v>
+        <v>0.3611462343792964</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,51 +3326,51 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.4017940414076895</v>
+        <v>1.041070616326451</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6561</v>
+        <v>6526</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>424.4444375160064</v>
+        <v>424.5874808937812</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>323</v>
+        <v>572</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G55" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46.75379393861002</v>
+        <v>42.82993963588281</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.2879564790108</v>
+        <v>15.0320740204058</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6974412670260183</v>
+        <v>0.8205686937221662</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0485607504468919</v>
+        <v>-0.4017940414076895</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6683</v>
+        <v>6561</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>422.3336358417728</v>
+        <v>424.4444375160064</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1140</v>
+        <v>323</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>42.7721725266835</v>
+        <v>46.75379393861002</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.07843058528049</v>
+        <v>13.2879564790108</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.83370426077422</v>
+        <v>0.6974412670260183</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>22.2545969057318</v>
+        <v>0.0485607504468919</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6829</v>
+        <v>6683</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>420.5384633394289</v>
+        <v>422.3336358417728</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>214</v>
+        <v>1140</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.47032566346078</v>
+        <v>42.7721725266835</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>17.18442002380276</v>
+        <v>19.07843058528049</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7039281008455075</v>
+        <v>1.83370426077422</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>3.440317966272027</v>
+        <v>22.2545969057318</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6811</v>
+        <v>6829</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>417.4604408006276</v>
+        <v>420.5384633394289</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.31793241884244</v>
+        <v>52.47032566346078</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15.2516984187485</v>
+        <v>17.18442002380276</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.1683844454762003</v>
+        <v>0.7039281008455075</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.028304493521528</v>
+        <v>3.440317966272027</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6664</v>
+        <v>6811</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>415.9587015972379</v>
+        <v>417.4604408006276</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>331.5</v>
+        <v>226</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>42.93967870034276</v>
+        <v>48.31793241884244</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.45854611145377</v>
+        <v>15.2516984187485</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4134243814784409</v>
+        <v>0.1683844454762003</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,51 +3591,51 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1341295887620965</v>
+        <v>-1.028304493521528</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6658</v>
+        <v>6664</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>410.6547403191383</v>
+        <v>415.9587015972379</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>161</v>
+        <v>331.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.12060848432098</v>
+        <v>42.93967870034276</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>13.47864762885178</v>
+        <v>22.45854611145377</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4810770372334185</v>
+        <v>0.4134243814784409</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>2.111438305277221</v>
+        <v>0.1341295887620965</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6550</v>
+        <v>6658</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>405.7922077599196</v>
+        <v>410.6547403191383</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>12.25</v>
+        <v>161</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>58.38041761667116</v>
+        <v>49.12060848432098</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>27.36968754818258</v>
+        <v>13.47864762885178</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.260542853344034</v>
+        <v>0.4810770372334185</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,51 +3697,51 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1427108538929399</v>
+        <v>2.111438305277221</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, bb_squeeze_breakout, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6679</v>
+        <v>6550</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>394.0078758344191</v>
+        <v>405.7922077599196</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>200</v>
+        <v>12.25</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G62" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>37.36081766906948</v>
+        <v>58.38041761667116</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27.54614826498131</v>
+        <v>27.36968754818258</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5702064874310817</v>
+        <v>1.260542853344034</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.6871201775528313</v>
+        <v>0.1427108538929399</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, bb_squeeze_breakout, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6485</v>
+        <v>6679</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>384.6049849122351</v>
+        <v>394.0078758344191</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>39.96931008865982</v>
+        <v>37.36081766906948</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>24.19998809118429</v>
+        <v>27.54614826498131</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4418443354498296</v>
+        <v>0.5702064874310817</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.6533556109991698</v>
+        <v>0.6871201775528313</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6823</v>
+        <v>6485</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>376.8975586563032</v>
+        <v>384.6049849122351</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>62.9</v>
+        <v>60</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45.19204170316485</v>
+        <v>39.96931008865982</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.75125696951025</v>
+        <v>24.19998809118429</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.135078397381681</v>
+        <v>0.4418443354498296</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0043027814105989</v>
+        <v>0.6533556109991698</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6642</v>
+        <v>6823</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>370.1746292869607</v>
+        <v>376.8975586563032</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>78.5</v>
+        <v>62.9</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47.63044669352949</v>
+        <v>45.19204170316485</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18.43631520260429</v>
+        <v>14.75125696951025</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.8177429549655328</v>
+        <v>2.135078397381681</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,51 +3909,51 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.07955390687050561</v>
+        <v>-0.0043027814105989</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6606</v>
+        <v>6642</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>366.5258542763498</v>
+        <v>370.1746292869607</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>25.65</v>
+        <v>78.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G66" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>41.67524051825248</v>
+        <v>47.63044669352949</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14.1229629887438</v>
+        <v>18.43631520260429</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.554956439317286</v>
+        <v>0.8177429549655328</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.1110072220006474</v>
+        <v>0.07955390687050561</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6835</v>
+        <v>6606</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>365.1493480880353</v>
+        <v>366.5258542763498</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>31.1</v>
+        <v>25.65</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>43.23735764758984</v>
+        <v>41.67524051825248</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>25.757747891842</v>
+        <v>14.1229629887438</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3864050561323667</v>
+        <v>0.554956439317286</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,48 +4015,48 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.1821346269316465</v>
+        <v>-0.1110072220006474</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6654</v>
+        <v>6835</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>363.0339983317173</v>
+        <v>365.1493480880353</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>166</v>
+        <v>31.1</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G68" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45.51972774630168</v>
+        <v>43.23735764758984</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.90574260052982</v>
+        <v>25.757747891842</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3500093138251033</v>
+        <v>0.3864050561323667</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.2396021067211307</v>
+        <v>0.1821346269316465</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6739</v>
+        <v>6654</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>362.549076806375</v>
+        <v>363.0339983317173</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>978</v>
+        <v>166</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45.5193413608396</v>
+        <v>45.51972774630168</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>9.07153619414683</v>
+        <v>15.90574260052982</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4567303354181227</v>
+        <v>0.3500093138251033</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,48 +4121,48 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>4.273977929821982</v>
+        <v>-0.2396021067211307</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6781</v>
+        <v>6739</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>360.2947619357996</v>
+        <v>362.549076806375</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1050</v>
+        <v>978</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G70" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>47.31557021568482</v>
+        <v>45.5193413608396</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15.52048739882272</v>
+        <v>9.07153619414683</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3940641539731317</v>
+        <v>0.4567303354181227</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.4946456896939128</v>
+        <v>4.273977929821982</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4184,38 +4184,38 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6643</v>
+        <v>6781</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>357.1049811046137</v>
+        <v>360.2947619357996</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>409</v>
+        <v>1050</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G71" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>42.38599966533889</v>
+        <v>47.31557021568482</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.86206753827163</v>
+        <v>15.52048739882272</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2666171564879682</v>
+        <v>0.3940641539731317</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.319394389231757</v>
+        <v>0.4946456896939128</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6530</v>
+        <v>6643</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>356.3144889595067</v>
+        <v>357.1049811046137</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>409</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.8555200639255</v>
+        <v>42.38599966533889</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.33106403429162</v>
+        <v>15.86206753827163</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6196967545088254</v>
+        <v>0.2666171564879682</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1.167455141706495</v>
+        <v>0.319394389231757</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4290,41 +4290,41 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6515</v>
+        <v>6530</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>351.7721689679119</v>
+        <v>356.3144889595067</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>6400</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>43.62148866023647</v>
+        <v>52.8555200639255</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.34353265672638</v>
+        <v>18.33106403429162</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5434744812973946</v>
+        <v>0.6196967545088254</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,48 +4333,48 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>46.37545284254665</v>
+        <v>1.167455141706495</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6570</v>
+        <v>6515</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>351.1459693008643</v>
+        <v>351.7721689679119</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>55</v>
+        <v>6400</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G74" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>53.87906795396366</v>
+        <v>43.62148866023647</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15.2018624491106</v>
+        <v>15.34353265672638</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6029835782872506</v>
+        <v>0.5434744812973946</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0652592247980958</v>
+        <v>46.37545284254665</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6568</v>
+        <v>6570</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>350.9721465222248</v>
+        <v>351.1459693008643</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>33.78697399487096</v>
+        <v>53.87906795396366</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>48.5401053648716</v>
+        <v>15.2018624491106</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5241357577667417</v>
+        <v>0.6029835782872506</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,51 +4439,51 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.3786252280235516</v>
+        <v>-0.0652592247980958</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6706</v>
+        <v>6568</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>350.8125202912633</v>
+        <v>350.9721465222248</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>116.5</v>
+        <v>126</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G76" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.97030522728056</v>
+        <v>33.78697399487096</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.78312424963021</v>
+        <v>48.5401053648716</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.517217610765306</v>
+        <v>0.5241357577667417</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,48 +4492,48 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>2.144824889600787</v>
+        <v>0.3786252280235516</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6693</v>
+        <v>6706</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>347.7393564526542</v>
+        <v>350.8125202912633</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>169</v>
+        <v>116.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G77" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>44.01102290568019</v>
+        <v>47.97030522728056</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.58788990897505</v>
+        <v>16.78312424963021</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.040306203563394</v>
+        <v>0.517217610765306</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,48 +4545,48 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>1.269412355699895</v>
+        <v>2.144824889600787</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6525</v>
+        <v>6693</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>344.3921680977695</v>
+        <v>347.7393564526542</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G78" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45.44670869453704</v>
+        <v>44.01102290568019</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.75815785135854</v>
+        <v>17.58788990897505</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4958549988875829</v>
+        <v>1.040306203563394</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.831060172639146</v>
+        <v>1.269412355699895</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4608,38 +4608,38 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6548</v>
+        <v>6525</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>344.1837938197897</v>
+        <v>344.3921680977695</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>138</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G79" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45.04587798584046</v>
+        <v>45.44670869453704</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.10090030353978</v>
+        <v>13.75815785135854</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5204813203511389</v>
+        <v>0.4958549988875829</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.3088298378120593</v>
+        <v>0.831060172639146</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4661,38 +4661,38 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6585</v>
+        <v>6548</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>340.2181169981936</v>
+        <v>344.1837938197897</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>116.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.16034850842024</v>
+        <v>45.04587798584046</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15.47163577633516</v>
+        <v>13.10090030353978</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.2907906469988909</v>
+        <v>0.5204813203511389</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,48 +4704,48 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1013336362218391</v>
+        <v>0.3088298378120593</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6486</v>
+        <v>6585</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>327.7486984779076</v>
+        <v>340.2181169981936</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>73.8</v>
+        <v>116.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G81" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>35.64771017648491</v>
+        <v>47.16034850842024</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>23.38669402535176</v>
+        <v>15.47163577633516</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4968218178852125</v>
+        <v>0.2907906469988909</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.172227903380715</v>
+        <v>0.1013336362218391</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6560</v>
+        <v>6486</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>325.6915340441612</v>
+        <v>327.7486984779076</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>31.55</v>
+        <v>73.8</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>39.31027844925903</v>
+        <v>35.64771017648491</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>23.21641984655206</v>
+        <v>23.38669402535176</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.11927011968089</v>
+        <v>0.4968218178852125</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.118577008144509</v>
+        <v>0.172227903380715</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6690</v>
+        <v>6560</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>309.7416841431191</v>
+        <v>325.6915340441612</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>162.5</v>
+        <v>31.55</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46.40570696119065</v>
+        <v>39.31027844925903</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>14.79631171157742</v>
+        <v>23.21641984655206</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6559590481989858</v>
+        <v>0.11927011968089</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,51 +4863,51 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.1639698887361866</v>
+        <v>0.118577008144509</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6757</v>
+        <v>6690</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>307.2882988564275</v>
+        <v>309.7416841431191</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>55.8</v>
+        <v>162.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G84" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.2748011678178</v>
+        <v>46.40570696119065</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>9.920972009691177</v>
+        <v>14.79631171157742</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.86816093814871</v>
+        <v>0.6559590481989858</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1160684753700427</v>
+        <v>0.1639698887361866</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6657</v>
+        <v>6757</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>306.4488912257873</v>
+        <v>307.2882988564275</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>30.6</v>
+        <v>55.8</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>42.6359719524287</v>
+        <v>47.2748011678178</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>28.31895641414194</v>
+        <v>9.920972009691177</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.784346044808793</v>
+        <v>0.86816093814871</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.1376920377481203</v>
+        <v>0.1160684753700427</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6698</v>
+        <v>6657</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>304.3058113435625</v>
+        <v>306.4488912257873</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>31.4</v>
+        <v>30.6</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>39.60014928282891</v>
+        <v>42.6359719524287</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>26.50031818659725</v>
+        <v>28.31895641414194</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4875016236690591</v>
+        <v>0.784346044808793</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1063655726379577</v>
+        <v>0.1376920377481203</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6592</v>
+        <v>6698</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>304.1219578206797</v>
+        <v>304.3058113435625</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>61.5</v>
+        <v>31.4</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>54.23652559963989</v>
+        <v>39.60014928282891</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>9.383830426778143</v>
+        <v>26.50031818659725</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.534807275646891</v>
+        <v>0.4875016236690591</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,48 +5075,48 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.080574898621654</v>
+        <v>0.1063655726379577</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6546</v>
+        <v>6592</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>298.3003292049061</v>
+        <v>304.1219578206797</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>62.1</v>
+        <v>61.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G88" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.25427658354482</v>
+        <v>54.23652559963989</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>22.4463090245697</v>
+        <v>9.383830426778143</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4723475333869855</v>
+        <v>1.534807275646891</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,48 +5128,48 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.68382285823319</v>
+        <v>0.080574898621654</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6719</v>
+        <v>6546</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>297.4101067015472</v>
+        <v>298.3003292049061</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>193.5</v>
+        <v>62.1</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G89" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>36.63882247305807</v>
+        <v>49.25427658354482</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.37954911935453</v>
+        <v>22.4463090245697</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.4304637716324297</v>
+        <v>0.4723475333869855</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0493776042723261</v>
+        <v>0.68382285823319</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6671</v>
+        <v>6719</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>296.2237951021078</v>
+        <v>297.4101067015472</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>23.05</v>
+        <v>193.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>48.05818142641479</v>
+        <v>36.63882247305807</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>27.14066680668775</v>
+        <v>22.37954911935453</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4154513926591627</v>
+        <v>0.4304637716324297</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,48 +5234,48 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1257783196410224</v>
+        <v>0.0493776042723261</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6640</v>
+        <v>6671</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>294.1846430169996</v>
+        <v>296.2237951021078</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>954</v>
+        <v>23.05</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G91" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>47.89763535199406</v>
+        <v>48.05818142641479</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>19.03599685524829</v>
+        <v>27.14066680668775</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7968444518985808</v>
+        <v>0.4154513926591627</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,48 +5287,48 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>13.65149520334221</v>
+        <v>0.1257783196410224</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6689</v>
+        <v>6640</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>293.2193903615967</v>
+        <v>294.1846430169996</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>61.1</v>
+        <v>954</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G92" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>47.69060284672123</v>
+        <v>47.89763535199406</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16.40257893875873</v>
+        <v>19.03599685524829</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.392409485793364</v>
+        <v>0.7968444518985808</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.1084674758167966</v>
+        <v>13.65149520334221</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6768</v>
+        <v>6689</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>290.3288271563379</v>
+        <v>293.2193903615967</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>65.2</v>
+        <v>61.1</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>37.54461421203273</v>
+        <v>47.69060284672123</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>34.70750827415874</v>
+        <v>16.40257893875873</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5126641301322565</v>
+        <v>0.392409485793364</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.236132767007938</v>
+        <v>0.1084674758167966</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6668</v>
+        <v>6768</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>288.7893656405135</v>
+        <v>290.3288271563379</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>36.4</v>
+        <v>65.2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>51.74450599873563</v>
+        <v>37.54461421203273</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17.91007271824378</v>
+        <v>34.70750827415874</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3529002952823957</v>
+        <v>0.5126641301322565</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,51 +5446,51 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.2135440641101931</v>
+        <v>0.236132767007938</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6684</v>
+        <v>6668</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>282.9845529785097</v>
+        <v>288.7893656405135</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>46.45</v>
+        <v>36.4</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G95" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>40.67964929571788</v>
+        <v>51.74450599873563</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.01819641718708</v>
+        <v>17.91007271824378</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.416925082405908</v>
+        <v>0.3529002952823957</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0214393675901862</v>
+        <v>0.2135440641101931</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6613</v>
+        <v>6684</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>281.6198755223919</v>
+        <v>282.9845529785097</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>253</v>
+        <v>46.45</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>36.99174498110574</v>
+        <v>40.67964929571788</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12.11615311218881</v>
+        <v>13.01819641718708</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4561988148021575</v>
+        <v>0.416925082405908</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,48 +5552,48 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.493769197627174</v>
+        <v>-0.0214393675901862</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6531</v>
+        <v>6613</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>280.575663615958</v>
+        <v>281.6198755223919</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>883</v>
+        <v>253</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G97" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>51.88027669588073</v>
+        <v>36.99174498110574</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>10.80924593396965</v>
+        <v>12.11615311218881</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.262012205769545</v>
+        <v>0.4561988148021575</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>8.628499262858298</v>
+        <v>-1.493769197627174</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6691</v>
+        <v>6531</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>278.4156313212669</v>
+        <v>280.575663615958</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>593</v>
+        <v>883</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>29.94659019201477</v>
+        <v>51.88027669588073</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.84226389194361</v>
+        <v>10.80924593396965</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.342742310340414</v>
+        <v>1.262012205769545</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-10.5802454642649</v>
+        <v>8.628499262858298</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6534</v>
+        <v>6691</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>277.2806491496095</v>
+        <v>278.4156313212669</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>92.3</v>
+        <v>593</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.26689832523215</v>
+        <v>29.94659019201477</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>19.55050089340641</v>
+        <v>17.84226389194361</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2121404887403639</v>
+        <v>1.342742310340414</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,48 +5711,48 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.3309061528629515</v>
+        <v>-10.5802454642649</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6667</v>
+        <v>6534</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>275.5228398498988</v>
+        <v>277.2806491496095</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>223</v>
+        <v>92.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G100" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>40.78362669706191</v>
+        <v>46.26689832523215</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>28.13927759599618</v>
+        <v>19.55050089340641</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3687278299670776</v>
+        <v>0.2121404887403639</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.6890975965834718</v>
+        <v>-0.3309061528629515</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6556</v>
+        <v>6667</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>275.1670214489205</v>
+        <v>275.5228398498988</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>58.5</v>
+        <v>223</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>32.50907175579084</v>
+        <v>40.78362669706191</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>20.8323086766569</v>
+        <v>28.13927759599618</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.497184889211769</v>
+        <v>0.3687278299670776</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.4128938046718748</v>
+        <v>0.6890975965834718</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,38 +5827,38 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6792</v>
+        <v>6556</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>274.7869915055505</v>
+        <v>275.1670214489205</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>58.8</v>
+        <v>58.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G102" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>54.17731489749863</v>
+        <v>32.50907175579084</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.22915221852184</v>
+        <v>20.8323086766569</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4116406971409324</v>
+        <v>0.497184889211769</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.5471523886907071</v>
+        <v>-0.4128938046718748</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6504</v>
+        <v>6792</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>272.6575939455087</v>
+        <v>274.7869915055505</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>38.3</v>
+        <v>58.8</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>52.20591042209099</v>
+        <v>54.17731489749863</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>21.7813777269828</v>
+        <v>13.22915221852184</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.087852990763935</v>
+        <v>0.4116406971409324</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.206896245455326</v>
+        <v>0.5471523886907071</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6579</v>
+        <v>6504</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>271.6380823708195</v>
+        <v>272.6575939455087</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>148</v>
+        <v>38.3</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>39.89732998917179</v>
+        <v>52.20591042209099</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>11.8867662257637</v>
+        <v>21.7813777269828</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3771958351883016</v>
+        <v>1.087852990763935</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-1.857837905805827</v>
+        <v>-0.206896245455326</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6573</v>
+        <v>6579</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>258.3073209171596</v>
+        <v>271.6380823708195</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>17.1</v>
+        <v>148</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.94313208359216</v>
+        <v>39.89732998917179</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.62914686467726</v>
+        <v>11.8867662257637</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6109552781719284</v>
+        <v>0.3771958351883016</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.1082202542224242</v>
+        <v>-1.857837905805827</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6558</v>
+        <v>6573</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>253.0139126931936</v>
+        <v>258.3073209171596</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>24.65</v>
+        <v>17.1</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.96874958670926</v>
+        <v>45.94313208359216</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>29.11562835992342</v>
+        <v>13.62914686467726</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3157103764244502</v>
+        <v>0.6109552781719284</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0411558788263727</v>
+        <v>0.1082202542224242</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6743</v>
+        <v>6558</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>245.8501050729468</v>
+        <v>253.0139126931936</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>25.2</v>
+        <v>24.65</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>36.60645667007992</v>
+        <v>38.96874958670926</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>26.01176068392601</v>
+        <v>29.11562835992342</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.2354161642165582</v>
+        <v>0.3157103764244502</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,48 +6135,48 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1576337886762557</v>
+        <v>0.0411558788263727</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6732</v>
+        <v>6743</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>238.3731403605633</v>
+        <v>245.8501050729468</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>150.5</v>
+        <v>25.2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G108" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>37.6188847518737</v>
+        <v>36.60645667007992</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>20.69046758996113</v>
+        <v>26.01176068392601</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4046075327113885</v>
+        <v>0.2354161642165582</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,48 +6188,48 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1249494319417134</v>
+        <v>-0.1576337886762557</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6838</v>
+        <v>6732</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>231.2748577507581</v>
+        <v>238.3731403605633</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>23.2</v>
+        <v>150.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G109" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.59093781914716</v>
+        <v>37.6188847518737</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.06063843899097</v>
+        <v>20.69046758996113</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.301461826771295</v>
+        <v>0.4046075327113885</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,51 +6241,51 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.009790516814467401</v>
+        <v>-0.1249494319417134</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6735</v>
+        <v>6838</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>229.0154847218473</v>
+        <v>231.2748577507581</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>63.5</v>
+        <v>23.2</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G110" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>41.92553118871661</v>
+        <v>46.59093781914716</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>20.61465616840031</v>
+        <v>10.06063843899097</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4981311862631876</v>
+        <v>0.301461826771295</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,51 +6294,51 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.6834303700809929</v>
+        <v>0.009790516814467401</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6695</v>
+        <v>6735</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>224.9490600022244</v>
+        <v>229.0154847218473</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>47.45</v>
+        <v>63.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G111" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>39.88122181647316</v>
+        <v>41.92553118871661</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>15.85861896719878</v>
+        <v>20.61465616840031</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4140918555749022</v>
+        <v>0.4981311862631876</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0731084912256727</v>
+        <v>0.6834303700809929</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6552</v>
+        <v>6695</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>223.9608056836623</v>
+        <v>224.9490600022244</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>24.85</v>
+        <v>47.45</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.88853374354063</v>
+        <v>39.88122181647316</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.60633260973175</v>
+        <v>15.85861896719878</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.2912706602825299</v>
+        <v>0.4140918555749022</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.23599773617578</v>
+        <v>-0.0731084912256727</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6799</v>
+        <v>6552</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>222.0137526718956</v>
+        <v>223.9608056836623</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>24.85</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>41.49083333584894</v>
+        <v>44.88853374354063</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.48094486779489</v>
+        <v>16.60633260973175</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.2088729789805504</v>
+        <v>0.2912706602825299</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1071912865127604</v>
+        <v>0.23599773617578</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6655</v>
+        <v>6799</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>214.5511361356334</v>
+        <v>222.0137526718956</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>116</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.60731470300963</v>
+        <v>41.49083333584894</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>8.533444144816137</v>
+        <v>17.48094486779489</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.1829018211646029</v>
+        <v>0.2088729789805504</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.1908521449878015</v>
+        <v>-0.1071912865127604</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6754</v>
+        <v>6655</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>211.2576150642717</v>
+        <v>214.5511361356334</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>42.4</v>
+        <v>116</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>51.16340397411792</v>
+        <v>46.60731470300963</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>10.73930513458722</v>
+        <v>8.533444144816137</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.564703998719129</v>
+        <v>0.1829018211646029</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,51 +6559,51 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0533567072518598</v>
+        <v>-0.1908521449878015</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6725</v>
+        <v>6754</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>209.5092384194803</v>
+        <v>211.2576150642717</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>226.5</v>
+        <v>42.4</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G116" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>30.97007931528856</v>
+        <v>51.16340397411792</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>28.18437209019873</v>
+        <v>10.73930513458722</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.517357608213986</v>
+        <v>0.564703998719129</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,51 +6612,51 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2069000164864789</v>
+        <v>0.0533567072518598</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6722</v>
+        <v>6725</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>208.7927815693194</v>
+        <v>209.5092384194803</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>32.45</v>
+        <v>226.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G117" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>38.64826934642853</v>
+        <v>30.97007931528856</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>43.89464006974928</v>
+        <v>28.18437209019873</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4362292158853717</v>
+        <v>0.517357608213986</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0350874013656453</v>
+        <v>-0.2069000164864789</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6742</v>
+        <v>6722</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>197.1626362460816</v>
+        <v>208.7927815693194</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>44.5</v>
+        <v>32.45</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45.44754056722193</v>
+        <v>38.64826934642853</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>18.0665571282736</v>
+        <v>43.89464006974928</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.3707740284479074</v>
+        <v>0.4362292158853717</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.6388443385607583</v>
+        <v>0.0350874013656453</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6591</v>
+        <v>6742</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>194.4239680795098</v>
+        <v>197.1626362460816</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>42.85</v>
+        <v>44.5</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>37.67216142000753</v>
+        <v>45.44754056722193</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>34.41271806125216</v>
+        <v>18.0665571282736</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4722722595868071</v>
+        <v>0.3707740284479074</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.1512233982150879</v>
+        <v>0.6388443385607583</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6776</v>
+        <v>6591</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>187.3748994644502</v>
+        <v>194.4239680795098</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>53.5</v>
+        <v>42.85</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>45.46338264410712</v>
+        <v>37.67216142000753</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.89361355172325</v>
+        <v>34.41271806125216</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.2022339862642549</v>
+        <v>0.4722722595868071</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0391479359447282</v>
+        <v>0.1512233982150879</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6614</v>
+        <v>6776</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>182.025130981759</v>
+        <v>187.3748994644502</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>35.95</v>
+        <v>53.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>37.11640969435806</v>
+        <v>45.46338264410712</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>11.16286349890504</v>
+        <v>17.89361355172325</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4516149587498641</v>
+        <v>0.2022339862642549</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0944487871438076</v>
+        <v>0.0391479359447282</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6794</v>
+        <v>6614</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>153.2711753289915</v>
+        <v>182.025130981759</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>71.8</v>
+        <v>35.95</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>41.50463057367911</v>
+        <v>37.11640969435806</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>20.82037187900118</v>
+        <v>11.16286349890504</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.221356089760626</v>
+        <v>0.4516149587498641</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.2203948849086658</v>
+        <v>0.0944487871438076</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6641</v>
+        <v>6794</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>150.7682604556138</v>
+        <v>153.2711753289915</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>17.85</v>
+        <v>71.8</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>47.73198115004521</v>
+        <v>41.50463057367911</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>9.278500210424196</v>
+        <v>20.82037187900118</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5464631591122421</v>
+        <v>1.221356089760626</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.035089720974453</v>
+        <v>-0.2203948849086658</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6581</v>
+        <v>6641</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>145.7499600784116</v>
+        <v>150.7682604556138</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>108.5</v>
+        <v>17.85</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>54.18350097621501</v>
+        <v>47.73198115004521</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.26713372947716</v>
+        <v>9.278500210424196</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.3610553028317755</v>
+        <v>0.5464631591122421</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.007792228829162</v>
+        <v>0.035089720974453</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6625</v>
+        <v>6581</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>139.3071263872351</v>
+        <v>145.7499600784116</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>76.3</v>
+        <v>108.5</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>47.20457685125452</v>
+        <v>54.18350097621501</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>10.05215641741904</v>
+        <v>17.26713372947716</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.5008804742117211</v>
+        <v>0.3610553028317755</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0048097189086848</v>
+        <v>-0.007792228829162</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6541</v>
+        <v>6625</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>127.5483814000781</v>
+        <v>139.3071263872351</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>36.95</v>
+        <v>76.3</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>43.62691228090349</v>
+        <v>47.20457685125452</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.4778628658852</v>
+        <v>10.05215641741904</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.7740332443052589</v>
+        <v>0.5008804742117211</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.07845230708680589</v>
+        <v>0.0048097189086848</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,52 +7152,105 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>6541</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>泰福-KY</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>127.5483814000781</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>43.62691228090349</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>11.4778628658852</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.7740332443052589</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.07845230708680589</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>6790</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>永豐實</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>91.13892786929658</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E128" s="2" t="n">
         <v>38.35</v>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>47.0237357691729</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>16.61082678218157</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J128" s="2" t="n">
         <v>0.4532683101155308</v>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>0.0597104190693082</v>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
